--- a/Formato_Evaluacion_Ponderada.xlsx
+++ b/Formato_Evaluacion_Ponderada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://its2sicgov-my.sharepoint.com/personal/jbohorquez_sic_gov_co/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://its2sicgov-my.sharepoint.com/personal/jbohorquez_sic_gov_co/Documents/Escritorio/ASUNTOS_JURISDICCIONALES/AUTOMATIZACIONES/APP_CALIFICACIÓN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{10BF16F1-33B9-45A9-8907-7E20EB1E3FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373E5C0A-796A-4DBE-9BDB-C068B6415934}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{10BF16F1-33B9-45A9-8907-7E20EB1E3FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A977AEA-7BC7-430D-B8C7-7A0B7702C0BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="43">
   <si>
     <t>Función</t>
   </si>
@@ -153,13 +153,49 @@
   </si>
   <si>
     <t>RESULTADO PONDERADO</t>
+  </si>
+  <si>
+    <t>ALCANTARA LOPEZ SANDRA VANNESA</t>
+  </si>
+  <si>
+    <t>CASTILLO CLAVIJO LEIDY LORENA</t>
+  </si>
+  <si>
+    <t>CASTILLO NIEVES NAYLA CONSUELO</t>
+  </si>
+  <si>
+    <t>FLOREZ CHARRY DANIELA SOFIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ PALMA JUAN DAVID</t>
+  </si>
+  <si>
+    <t>GUERRA HINOJOSA OCTAVIO JOSE</t>
+  </si>
+  <si>
+    <t>GUERRERO CHAVEZ DAVID ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JIMENEZ DORADO JUAN FERNANDO</t>
+  </si>
+  <si>
+    <t>PERÉZ RAMÍREZ FREDY ALEXANDER</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ DIAZ WILHELM FREDY</t>
+  </si>
+  <si>
+    <t>VALLEJO ARTEAGA MARÍA CRISTINA</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +233,14 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -260,7 +304,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,12 +324,27 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -583,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EB5B7B-637D-4873-82B2-4A0E8A5CF54F}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -766,8 +825,99 @@
         <v>1</v>
       </c>
     </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B22" xr:uid="{E1EB5B7B-637D-4873-82B2-4A0E8A5CF54F}"/>
+  <conditionalFormatting sqref="A23:A33">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
